--- a/output/pdf_financials_xlsx/BEI.UN.xlsx
+++ b/output/pdf_financials_xlsx/BEI.UN.xlsx
@@ -6802,7 +6802,7 @@
         <v>-0.05744</v>
       </c>
       <c r="K99" s="3" t="n">
-        <v>0.057258</v>
+        <v>-0.057258</v>
       </c>
       <c r="L99" s="3" t="n">
         <v>0.1932</v>
@@ -34121,7 +34121,7 @@
         <v>-0.05744</v>
       </c>
       <c r="N257" s="5" t="n">
-        <v>0.057258</v>
+        <v>-0.057258</v>
       </c>
       <c r="O257" t="inlineStr">
         <is>
@@ -59361,7 +59361,7 @@
         <v>-0.05744</v>
       </c>
       <c r="N513" s="5" t="n">
-        <v>0.057258</v>
+        <v>-0.057258</v>
       </c>
       <c r="O513" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/BEI.UN.xlsx
+++ b/output/pdf_financials_xlsx/BEI.UN.xlsx
@@ -1168,13 +1168,13 @@
         <v>0</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.000935</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.003059</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.012498</v>
       </c>
       <c r="R12" s="1" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         <v>0.228086</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.255894</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.138656</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>0.131079</v>
@@ -2827,10 +2827,10 @@
         <v>0.228086</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.255894</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.138656</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>0.131079</v>
@@ -3571,10 +3571,10 @@
         <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.271293</v>
+        <v>0.015399</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.154538</v>
+        <v>0.015882</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>0.016913</v>
@@ -20220,7 +20220,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -48192,7 +48192,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">

--- a/output/pdf_financials_xlsx/BEI.UN.xlsx
+++ b/output/pdf_financials_xlsx/BEI.UN.xlsx
@@ -1384,7 +1384,7 @@
         <v>0.112216</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1.225086</v>
+        <v>1.965477</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>0.688736</v>
@@ -1454,7 +1454,7 @@
         <v>-0.040487</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.740391</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>-0.000222</v>
@@ -2240,7 +2240,7 @@
         <v>0.112216</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1.225086</v>
+        <v>1.965477</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>0.688736</v>
@@ -2372,7 +2372,7 @@
         <v>0.112216</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>1.235606</v>
+        <v>1.975997</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>0.699658</v>
@@ -2534,7 +2534,7 @@
         <v>36.0795252013973</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>37.66978702879759</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>0.0322329600892069</v>
@@ -5006,16 +5006,16 @@
         </is>
       </c>
       <c r="N70" s="3" t="n">
-        <v>0</v>
+        <v>0.003909</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>0</v>
+        <v>0.003396</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>0</v>
+        <v>0.002978</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>0</v>
+        <v>0.00321</v>
       </c>
       <c r="R70" s="1" t="inlineStr">
         <is>
@@ -5068,16 +5068,16 @@
         </is>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0.021187</v>
+        <v>0.025096</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>0</v>
+        <v>0.003396</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>0</v>
+        <v>0.002978</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>0</v>
+        <v>0.00321</v>
       </c>
       <c r="R71" s="1" t="inlineStr">
         <is>
@@ -5316,16 +5316,16 @@
         </is>
       </c>
       <c r="N75" s="3" t="n">
-        <v>0.5251670000000001</v>
+        <v>0.521258</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>0.524968</v>
+        <v>0.521572</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>0.926569</v>
+        <v>0.9235910000000001</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>1.052671</v>
+        <v>1.049461</v>
       </c>
       <c r="R75" s="1" t="inlineStr">
         <is>
@@ -5654,16 +5654,16 @@
         </is>
       </c>
       <c r="N80" s="3" t="n">
-        <v>0.02993042495676536</v>
+        <v>0.03113201921321243</v>
       </c>
       <c r="O80" s="3" t="n">
-        <v>0.02209461903352699</v>
+        <v>0.02307414079846599</v>
       </c>
       <c r="P80" s="3" t="n">
-        <v>0.01708721521307978</v>
+        <v>0.01777655557592559</v>
       </c>
       <c r="Q80" s="3" t="n">
-        <v>0.01502457508659118</v>
+        <v>0.01568823577693475</v>
       </c>
       <c r="R80" s="1" t="inlineStr">
         <is>
@@ -11236,7 +11236,11 @@
           <t>Lease liabilities 12</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -13051,7 +13055,11 @@
           <t>Lease liabilities 10</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -39091,7 +39099,11 @@
           <t>Future income taxes (recovery)</t>
         </is>
       </c>
-      <c r="D308" t="inlineStr"/>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E308" s="5" t="n">
         <v>0.315</v>
       </c>
@@ -45344,7 +45356,11 @@
           <t>Future income taxes – – 100,287</t>
         </is>
       </c>
-      <c r="D371" t="inlineStr"/>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E371" s="5" t="n">
         <v>94.956</v>
       </c>
@@ -65147,7 +65163,11 @@
           <t>Profit from continuing operations before fair value gains and income tax recovery</t>
         </is>
       </c>
-      <c r="D572" t="inlineStr"/>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E572" t="inlineStr">
         <is>
           <t>-</t>
@@ -65446,7 +65466,11 @@
           <t>Profit before income tax recovery</t>
         </is>
       </c>
-      <c r="D575" t="inlineStr"/>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E575" t="inlineStr">
         <is>
           <t>-</t>
@@ -65545,7 +65569,11 @@
           <t>Income tax recovery 16</t>
         </is>
       </c>
-      <c r="D576" t="inlineStr"/>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E576" t="inlineStr">
         <is>
           <t>-</t>
